--- a/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,295 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 여기 온 이유는, 제 턱이랑 얼굴 한쪽이 어떻게 보이는지에 계속 신경이 쓰여서예요. 특히 가족사진 여러 장에서 제 모습을 보고 난 후로, 좀 처지고 비대칭인 것 같아요. 아내랑 고객들도 거의 눈치 못 챈다고 하는데, 저는 계속 거기에 집중하게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 턱이나 얼굴이 어떻게 보이는지 고치거나 확인하려고 반복해서 하시는 행동이 있나요? 만지거나, 자세를 고치거나, 거울을 자주 확인하는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 네, 그래요. 고객을 만나기 전에는 보통 화장실 거울을 확인하고, 그다음엔 휴대폰 카메라도 확인해요, 가끔은 몇 번씩이요. 조명을 조정하거나 더 나아 보이는지 얼굴을 이리저리 돌려봐요.
+깃도 고쳐 매고, 턱을 특정한 방식으로 들려고도 해요. 그리고 갤러리 행사나 다른 자문가들 사이에 있을 때는, 대화에 집중하는 대신 제 얼굴을 그들과 비교하고 있는 저 자신을 발견해요, 특히 젊은 사람들이랑요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 얼굴에 대한 이런 걱정들이 업무나 인간관계, 삶의 다른 영역에 지장을 주거나, 다른 사람들이 안심시켜 줘도 큰 괴로움을 주나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네, 어느 정도는 지장을 줘요. 그러니까, 저는 여전히 일도 하고 약속에도 나가는데, 고객 미팅에 나가기 전에 외모를 확인하거나 그걸로 마음을 편하게 하려고 하느라 느려졌어요.
+그리고 어떤 약속에서는 제가 있어야 할 만큼 온전히 집중하지 못해요. 제 마음 한편은 그들이 제 얼굴을 알아채는지에 가 있어요. 몇몇 미술 전시 오프닝도 사람들 눈에 띄거나 사진에 찍히기 싫어서 빠졌고요. 그러니까 제 삶 전체를 멈추게 하는 건 아니지만, 영향을 미치고는 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 미팅이나 행사에서 얼굴이 어떻게 보일지 걱정하실 때, 다른 사람들이 당신을 판단하거나 외모에 대해 부정적으로 생각한다고 불안하게 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 사람들이 그걸 본다고 걱정해요. 주로 턱이랑 얼굴 한쪽이 처지고 비대칭인 것 같은 부분이요. 그 가족사진들에서 그걸 알아챈 이후로, 아내나 고객들이 거의 눈치 못 챈다고 해도 다른 사람들도 볼 수 있을 거라는 생각이 계속 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 얼굴 한쪽의 비대칭이나 처짐이 스스로를 비정상적이거나 매력 없어 보이게 만드는 결함이라고 믿으시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네... 그래요. 다른 사람들은 거의 못 느낀다고 하는 걸 알지만, 저한테는 진짜 결함처럼 보여요. 턱이랑 얼굴 한쪽이 처지거나 비대칭인 것처럼요, 그리고 그 가족사진에서 그걸 본 이후로 거기에 계속 꽂혀 있게 됐어요. 아내나 고객이 뚜렷하지 않다고 해도, 그것 때문에 제가 더 나이 들어 보이거나 매력 없어 보인다는 느낌이 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 거울을 보거나 자신의 사진을 볼 때, 다른 사람들이 아니라고 해도 그 비대칭이나 처짐을 다른 사람들도 알아차려야 할 만한 큰 결함으로 보시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네... 그게 제가 여기 온 이유예요. 거울을 보거나 사진을 볼 때, 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀요. 저한테는 정말 뚜렷하게 느껴져요, 아내와 고객들이 거의 못 느낀다고 말해도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 얼굴을 보면서 비대칭이나 처짐에 집중할 때, 눈에 보이게 뭔가 잘못됐고 다른 사람들도 봐야 한다고 믿으시나요, 아니면 본인만 알아차리고 걱정하는 거라고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 눈에 보이게 뭔가 잘못됐다는 느낌이 들어요, 네. 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀 있어요. 그 가족사진에서 제 모습을 본 이후로 정말 눈에 띄었어요. 아내와 고객들이 거의 못 느낀다고 해도, 저는 여전히 그게 거기 있고 다른 사람들도 볼 수 있어야 한다고 느껴요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 하루에 턱과 얼굴이 어떻게 보이는지 생각하거나 확인하는 데 얼마나 시간을 쓰신다고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 아마 인정하고 싶은 것보다 많을 거예요. 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀요, 특히 그 가족사진들을 본 이후로요. 하루 중에도 자주 떠올라요, 아내와 고객들이 거의 못 느낀다고 해도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 하루에 턱과 얼굴이 어떻게 보이는지 생각하거나 확인하는 데 쓰시는 시간을 좀 더 구체적으로 추측해 주실 수 있을까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 정확한 숫자로 말하긴 어려운데, 평범한 날에는 아마 총 한두 시간 정도일 거예요. 고객 미팅 전에는 화장실 거울을 확인하고 휴대폰 카메라도 몇 번씩 확인해요, 조명을 조정하거나 깃을 바꾸거나 얼굴을 특정 각도로 돌려보기도 하고요. 그리고 행사나 미팅에서는 대화에 집중하는 대신 제 얼굴을 젊은 자문가들이나 거기 있는 사람들과 비교하는 저 자신을 발견해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 얼굴 한쪽의 처지거나 비대칭인 모습을 보면서, 뇌졸중이나 신경 문제 같은 의학적 상태와 관련이 있을지도 모른다고 생각해 보신 적이 있나요, 아니면 그것을 확인하기 위해 의학적 검사를 받아보신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 막연하게 뭔가 이상이 있을지도 모른다고 생각해 본 적은 있는데, 뇌졸중이나 신경 문제 관련해서 구체적으로 의학적 검사를 받아본 적은 없어요. 그냥 그걸 보고 그 모습에 신경이 쓰이는 쪽에 더 가까워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 얼굴 한쪽의 비대칭이나 처진 모습이 신체적으로 비정상적이거나 기형처럼 보이게 만든다고 믿으시나요, 아니면 눈에 띄게 결함이 있어 보이는 건 아니어도 대칭이 완벽하지 않다는 쪽에 가깝나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 기형이라고까지는 말 못하겠어요. 그보다는, 특히 사진에서 볼 때, 턱이랑 얼굴 한쪽이 얼마나 처지고 비대칭으로 보이는지에 꽂혀요. 저한테는 아주 두드러져 보여요, 아내와 고객들이 거의 못 느낀다고 해도요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 얼굴에 대한 걱정이 과하거나 비합리적이라고 느껴지시나요, 다른 사람들이 그걸 눈치채지 못하거나 문제라고 동의하지 않는데도요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 네, 그러니까... 제 마음 한편으로는 제가 다른 사람들이 보는 것보다 더 많이 신경 쓰고 있다는 걸 알아요. 아내와 고객들도 거의 못 느낀다고 하니까, 제가 이치에 맞는 것보다 더 거기에 꽂혀 있다는 걸 알 수 있어요.
+근데 사진을, 특히 그 가족사진들을 보면 정말로 턱이랑 얼굴 한쪽의 처지고 비대칭인 모습이 보이고, 그걸 놓아버리기가 힘들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 얼굴을 보면서 처지거나 비대칭인 모습에 집중하실 때, 대부분의 사람들은 그걸 사소하거나 거의 눈에 띄지 않는다고 여길 것 같으신가요, 아니면 다른 사람들도 분명한 결함으로 봐야 할 만큼 더 중요한 문제라고 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 대부분의 사람들은 아마 알아챈다고 해도 사소하다고 볼 것 같아요. 아내와 고객들도 거의 안 보인다고 하니까요. 하지만 저는 턱이랑 얼굴 한쪽의 처지고 비대칭인 모습에 계속 꽂혀 있어요, 특히 그 가족사진들 이후로요. 그냥 저한테는 두드러져 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 신체이형장애 (D017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>진단명: 신체이형장애 (D017)
 인구통계: 성별 남성 / 나이 45 / 직업상태 personal financial advisor / 최종학력 대학 재학
@@ -575,344 +855,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S067
-배경 서술: 아버지가 돌아가신 후, 에릭은 가족 사진과 장례 준비, 추모 슬라이드쇼를 정리하는 책임을 맡게 되었고, 그 과정에서 여러 해에 걸쳐 친척들과 함께 찍은 자신의 사진들을 직접 마주하게 되었다. 그 돌아보는 시기 동안, 그는 다른 사람들은 거의 눈치채지 못한다고 말하는 얼굴의 결함과 노화의 징후에 점점 더 집착하게 되었고, 고객 미팅 전에 외모를 확인하고 세련된 동료들과 갤러리 방문객들과 머릿속으로 비교하는 데 더 많은 시간을 쓰기 시작했다. 문제는 겉으로는 여전히 잘 억제되어 있었지만, 아침 일과를 늦추기 시작했고 몇몇 미술 전시 오프닝에 불참하게 만들었으며, 고객을 상대하는 업무 중에도 그의 주의를 분산시켜서 그 스스로도 업무적으로 비효율적이고 개인적으로 괴롭다고 인식할 정도가 되었다. 그는 정기 진료 중 조심스럽게 1차 진료의에게 이 문제를 언급했고 정신과 평가로 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 걸 환영합니다. 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 여기 온 이유는, 제 턱이랑 얼굴 한쪽이 어떻게 보이는지에 계속 신경이 쓰여서예요. 특히 가족사진 여러 장에서 제 모습을 보고 난 후로, 좀 처지고 비대칭인 것 같아요. 아내랑 고객들도 거의 눈치 못 챈다고 하는데, 저는 계속 거기에 집중하게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 턱이나 얼굴이 어떻게 보이는지 고치거나 확인하려고 반복해서 하시는 행동이 있나요? 만지거나, 자세를 고치거나, 거울을 자주 확인하는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 네, 그래요. 고객을 만나기 전에는 보통 화장실 거울을 확인하고, 그다음엔 휴대폰 카메라도 확인해요, 가끔은 몇 번씩이요. 조명을 조정하거나 더 나아 보이는지 얼굴을 이리저리 돌려봐요.
-깃도 고쳐 매고, 턱을 특정한 방식으로 들려고도 해요. 그리고 갤러리 행사나 다른 자문가들 사이에 있을 때는, 대화에 집중하는 대신 제 얼굴을 그들과 비교하고 있는 저 자신을 발견해요, 특히 젊은 사람들이랑요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 얼굴에 대한 이런 걱정들이 업무나 인간관계, 삶의 다른 영역에 지장을 주거나, 다른 사람들이 안심시켜 줘도 큰 괴로움을 주나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네, 어느 정도는 지장을 줘요. 그러니까, 저는 여전히 일도 하고 약속에도 나가는데, 고객 미팅에 나가기 전에 외모를 확인하거나 그걸로 마음을 편하게 하려고 하느라 느려졌어요.
-그리고 어떤 약속에서는 제가 있어야 할 만큼 온전히 집중하지 못해요. 제 마음 한편은 그들이 제 얼굴을 알아채는지에 가 있어요. 몇몇 미술 전시 오프닝도 사람들 눈에 띄거나 사진에 찍히기 싫어서 빠졌고요. 그러니까 제 삶 전체를 멈추게 하는 건 아니지만, 영향을 미치고는 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 미팅이나 행사에서 얼굴이 어떻게 보일지 걱정하실 때, 다른 사람들이 당신을 판단하거나 외모에 대해 부정적으로 생각한다고 불안하게 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 사람들이 그걸 본다고 걱정해요. 주로 턱이랑 얼굴 한쪽이 처지고 비대칭인 것 같은 부분이요. 그 가족사진들에서 그걸 알아챈 이후로, 아내나 고객들이 거의 눈치 못 챈다고 해도 다른 사람들도 볼 수 있을 거라는 생각이 계속 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 얼굴 한쪽의 비대칭이나 처짐이 스스로를 비정상적이거나 매력 없어 보이게 만드는 결함이라고 믿으시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네... 그래요. 다른 사람들은 거의 못 느낀다고 하는 걸 알지만, 저한테는 진짜 결함처럼 보여요. 턱이랑 얼굴 한쪽이 처지거나 비대칭인 것처럼요, 그리고 그 가족사진에서 그걸 본 이후로 거기에 계속 꽂혀 있게 됐어요. 아내나 고객이 뚜렷하지 않다고 해도, 그것 때문에 제가 더 나이 들어 보이거나 매력 없어 보인다는 느낌이 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 거울을 보거나 자신의 사진을 볼 때, 다른 사람들이 아니라고 해도 그 비대칭이나 처짐을 다른 사람들도 알아차려야 할 만한 큰 결함으로 보시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네... 그게 제가 여기 온 이유예요. 거울을 보거나 사진을 볼 때, 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀요. 저한테는 정말 뚜렷하게 느껴져요, 아내와 고객들이 거의 못 느낀다고 말해도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 얼굴을 보면서 비대칭이나 처짐에 집중할 때, 눈에 보이게 뭔가 잘못됐고 다른 사람들도 봐야 한다고 믿으시나요, 아니면 본인만 알아차리고 걱정하는 거라고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 눈에 보이게 뭔가 잘못됐다는 느낌이 들어요, 네. 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀 있어요. 그 가족사진에서 제 모습을 본 이후로 정말 눈에 띄었어요. 아내와 고객들이 거의 못 느낀다고 해도, 저는 여전히 그게 거기 있고 다른 사람들도 볼 수 있어야 한다고 느껴요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 하루에 턱과 얼굴이 어떻게 보이는지 생각하거나 확인하는 데 얼마나 시간을 쓰신다고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 아마 인정하고 싶은 것보다 많을 거예요. 턱이랑 얼굴 한쪽의 처지고 비대칭인 느낌에 계속 꽂혀요, 특히 그 가족사진들을 본 이후로요. 하루 중에도 자주 떠올라요, 아내와 고객들이 거의 못 느낀다고 해도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 하루에 턱과 얼굴이 어떻게 보이는지 생각하거나 확인하는 데 쓰시는 시간을 좀 더 구체적으로 추측해 주실 수 있을까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 정확한 숫자로 말하긴 어려운데, 평범한 날에는 아마 총 한두 시간 정도일 거예요. 고객 미팅 전에는 화장실 거울을 확인하고 휴대폰 카메라도 몇 번씩 확인해요, 조명을 조정하거나 깃을 바꾸거나 얼굴을 특정 각도로 돌려보기도 하고요. 그리고 행사나 미팅에서는 대화에 집중하는 대신 제 얼굴을 젊은 자문가들이나 거기 있는 사람들과 비교하는 저 자신을 발견해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 얼굴 한쪽의 처지거나 비대칭인 모습을 보면서, 뇌졸중이나 신경 문제 같은 의학적 상태와 관련이 있을지도 모른다고 생각해 보신 적이 있나요, 아니면 그것을 확인하기 위해 의학적 검사를 받아보신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 잘 모르겠어요. 막연하게 뭔가 이상이 있을지도 모른다고 생각해 본 적은 있는데, 뇌졸중이나 신경 문제 관련해서 구체적으로 의학적 검사를 받아본 적은 없어요. 그냥 그걸 보고 그 모습에 신경이 쓰이는 쪽에 더 가까워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 얼굴 한쪽의 비대칭이나 처진 모습이 신체적으로 비정상적이거나 기형처럼 보이게 만든다고 믿으시나요, 아니면 눈에 띄게 결함이 있어 보이는 건 아니어도 대칭이 완벽하지 않다는 쪽에 가깝나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 기형이라고까지는 말 못하겠어요. 그보다는, 특히 사진에서 볼 때, 턱이랑 얼굴 한쪽이 얼마나 처지고 비대칭으로 보이는지에 꽂혀요. 저한테는 아주 두드러져 보여요, 아내와 고객들이 거의 못 느낀다고 해도요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 얼굴에 대한 걱정이 과하거나 비합리적이라고 느껴지시나요, 다른 사람들이 그걸 눈치채지 못하거나 문제라고 동의하지 않는데도요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 네, 그러니까... 제 마음 한편으로는 제가 다른 사람들이 보는 것보다 더 많이 신경 쓰고 있다는 걸 알아요. 아내와 고객들도 거의 못 느낀다고 하니까, 제가 이치에 맞는 것보다 더 거기에 꽂혀 있다는 걸 알 수 있어요.
-근데 사진을, 특히 그 가족사진들을 보면 정말로 턱이랑 얼굴 한쪽의 처지고 비대칭인 모습이 보이고, 그걸 놓아버리기가 힘들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 얼굴을 보면서 처지거나 비대칭인 모습에 집중하실 때, 대부분의 사람들은 그걸 사소하거나 거의 눈에 띄지 않는다고 여길 것 같으신가요, 아니면 다른 사람들도 분명한 결함으로 봐야 할 만큼 더 중요한 문제라고 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 대부분의 사람들은 아마 알아챈다고 해도 사소하다고 볼 것 같아요. 아내와 고객들도 거의 안 보인다고 하니까요. 하지만 저는 턱이랑 얼굴 한쪽의 처지고 비대칭인 모습에 계속 꽂혀 있어요, 특히 그 가족사진들 이후로요. 그냥 저한테는 두드러져 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+배경 서술: 아버지가 돌아가신 후, 에릭은 가족 사진과 장례 준비, 추모 슬라이드쇼를 정리하는 책임을 맡게 되었고, 그 과정에서 여러 해에 걸쳐 친척들과 함께 찍은 자신의 사진들을 직접 마주하게 되었다. 그 돌아보는 시기 동안, 그는 다른 사람들은 거의 눈치채지 못한다고 말하는 얼굴의 결함과 노화의 징후에 점점 더 집착하게 되었고, 고객 미팅 전에 외모를 확인하고 세련된 동료들과 갤러리 방문객들과 머릿속으로 비교하는 데 더 많은 시간을 쓰기 시작했다. 문제는 겉으로는 여전히 잘 억제되어 있었지만, 아침 일과를 늦추기 시작했고 몇몇 미술 전시 오프닝에 불참하게 만들었으며, 고객을 상대하는 업무 중에도 그의 주의를 분산시켜서 그 스스로도 업무적으로 비효율적이고 개인적으로 괴롭다고 인식할 정도가 되었다. 그는 정기 진료 중 조심스럽게 1차 진료의에게 이 문제를 언급했고 정신과 평가로 의뢰되었다.
+표집된 증상 목록:
+  - S067 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - S068 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
+        </is>
+      </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>[13번째 턴 · 의사의 감별진단] 고확률: 신체이형장애 (D017)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.; 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 신체이형장애 (D017, ICD: F45.22)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: dysmorphic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 외모 집착: 타인에게는 관찰되지 않거나 경미하게 보이는 신체적 결함이나 흠에 대한 한 가지 이상의 집착.
+  - 외모 관련 반복 행동: 외모에 대한 걱정에 반응하여 수행하는 반복적 행동이나 정신적 활동.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
@@ -841,6 +841,11 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -875,11 +880,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D017_S003_P002__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
